--- a/series_data/footnotes/series_log.xlsx
+++ b/series_data/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,281 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep01/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-15 21:31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/686f6fa6dc55f4d259d756a3b4ad6aec_1784151080.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-15 21:39</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6b0a56a0195100e2ba76a03c7c836fc1_1784151220.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-15 21:44</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d121d0f7e735f0539a8abb99cd74549d_1784151850.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-15 21:48</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7281f991f4c801c9e5542495e2afd1bb_1784152029.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-15 21:50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/befc08467482525ff2be7fab9de3522b_1784152182.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep02/shots/shot_05.mp4</t>
         </is>
       </c>
     </row>

--- a/series_data/footnotes/series_log.xlsx
+++ b/series_data/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,281 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-16 21:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c58be316067cc326c42c93b7153c2866_1784237653.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16 21:37</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d2d766bc6ca48bb6fa50a72aa5ef18da_1784237812.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-16 21:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/606b64b38923b1476fb6a3337903be86_1784238421.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-16 21:57</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ae678d441224c03bbd0733ef795154b9_1784238983.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-16 22:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8555b54d646e93174831494db08c2bdb_1784239197.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep03/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/footnotes/series_log.xlsx
+++ b/series_data/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,281 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-17 21:23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/06a64f8006616d909534228a76b539d9_1784323359.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-17 21:26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/630fcf3a50dd301fca66416d8429b146_1784323539.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-17 21:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/79b1302dd9baaac69b2fb6d70ffe4377_1784323767.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-17 21:32</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ac66a0f02c6ed8348e40c206579377c5_1784323924.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-17 21:35</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c08550273363c3add950be1ac0b05cd3_1784324082.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep04/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
